--- a/config/tables/gas.effect.xlsx
+++ b/config/tables/gas.effect.xlsx
@@ -1,305 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect" sheetId="1" r:id="Rbe25a3cebadd4816"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">##var</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">duration_kind</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">duration_ticks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">period_ticks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">execute_on_applied</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">probability</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">asset_tags</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">granted_tags</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int#range=[1,1000000]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gas.DurationKind</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int?#range=[1,1000000]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">float#range=[0,1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(list#sep=;),string#ref=gas.TbTag</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##group</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unique effect identifier.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Designer effect name.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Instant, finite ticks, or infinite lifetime.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lifetime in fixed ticks. Required only for DurationTicks.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Execution period in fixed ticks. Blank disables periodic execution.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Execute the periodic effect immediately on application.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Application probability from zero to one.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Effect identity tags separated by semicolons.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tags granted while active, separated by semicolons.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fireball mana cost</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Instant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fireball cooldown</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DurationTicks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cooldown.Fireball</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fireball damage</x:t>
-  </x:si>
-</x:sst>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0###"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
   </numFmts>
   <fonts count="23">
     <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FF182238"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color rgb="FF182238"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="36">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -617,179 +505,183 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1038,7 +930,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1047,7 +939,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1060,11 +952,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1260,221 +1215,312 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="12" customWidth="1"/>
-    <x:col min="2" max="2" width="14" customWidth="1"/>
-    <x:col min="3" max="10" width="23" customWidth="1"/>
-    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K1" t="str" s="1">
-        <x:v>modifier_ids</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="52" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K2" t="str" s="2">
-        <x:v>(list#sep=;),(int#ref=gas.TbModifier)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B3" s="3"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="3"/>
-      <x:c r="F3" s="3"/>
-      <x:c r="G3" s="3"/>
-      <x:c r="H3" s="3"/>
-      <x:c r="I3" s="3"/>
-      <x:c r="J3" s="3"/>
-      <x:c r="K3" s="3"/>
-    </x:row>
-    <x:row r="4" ht="66" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="K4" t="str" s="4">
-        <x:v>Modifier IDs in application order. Blank means none.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="40" customHeight="1">
-      <x:c r="A5" s="5"/>
-      <x:c r="B5" s="6">
-        <x:v>2001</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E5" s="6"/>
-      <x:c r="F5" s="6"/>
-      <x:c r="G5" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I5" s="7"/>
-      <x:c r="J5" s="7"/>
-      <x:c r="K5" t="str" s="7">
-        <x:v>20101</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="5"/>
-      <x:c r="B6" s="6">
-        <x:v>2002</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E6" s="6">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F6" s="6"/>
-      <x:c r="G6" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I6" s="7"/>
-      <x:c r="J6" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K6" s="7"/>
-    </x:row>
-    <x:row r="7" ht="40" customHeight="1">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="6">
-        <x:v>2003</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E7" s="6"/>
-      <x:c r="F7" s="6"/>
-      <x:c r="G7" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I7" s="7"/>
-      <x:c r="J7" s="7"/>
-      <x:c r="K7" t="str" s="7">
-        <x:v>20301</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="D5:D7">
-      <x:formula1>"Instant,DurationTicks,Infinite"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="G5:G7">
-      <x:formula1>"TRUE,FALSE"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col width="12" customWidth="1" style="9" min="1" max="1"/>
+    <col width="14" customWidth="1" style="9" min="2" max="2"/>
+    <col width="23" customWidth="1" style="9" min="3" max="10"/>
+    <col width="30" customWidth="1" style="9" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="9">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>duration_kind</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>duration_ticks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>period_ticks</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>execute_on_applied</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>asset_tags</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>granted_tags</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>modifier_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1" s="9">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>int#range=[1,1000000]</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>gas.DurationKind</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>int?#range=[1,1000000]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>int?#range=[1,1000000]</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>float#range=[0,1]</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),string#ref=gas.TbTag</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),string#ref=gas.TbTag</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),(int#ref=gas.TbModifier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" s="9">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="66" customHeight="1" s="9">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Unique effect identifier.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Designer effect name.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Instant, finite ticks, or infinite lifetime.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Lifetime in fixed ticks. Required only for DurationTicks.</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Execution period in fixed ticks. Blank disables periodic execution.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Execute the periodic effect immediately on application.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Application probability from zero to one.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Effect identity tags separated by semicolons.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Tags granted while active, separated by semicolons.</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Modifier IDs in application order. Blank means none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1" s="9">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Laser mana cost</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>20101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" s="9">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Laser cooldown</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>DurationTicks</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Cooldown.Laser</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1" s="9">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Laser damage</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>20301</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="D5:D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Instant,DurationTicks,Infinite"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>